--- a/laporan_padel_dki_jakarta_2026-10-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-20.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.100.000</t>
+          <t>Rp14.280.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.219.500</t>
+          <t>Rp9.669.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.013.000</t>
+          <t>Rp3.211.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.285.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.142.000</t>
+          <t>Rp3.024.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.070.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp549.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.280.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.475.000</t>
+          <t>Rp7.662.500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.976.000</t>
+          <t>Rp3.274.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.480.000</t>
+          <t>Rp2.760.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.005.000</t>
+          <t>Rp4.385.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.545.000</t>
+          <t>Rp2.243.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp13.940.000</t>
+          <t>Rp14.270.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.600.000</t>
+          <t>Rp9.350.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp9.600.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp32.550.000</t>
+          <t>Rp32.300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.520.000</t>
+          <t>Rp11.660.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.673.000</t>
+          <t>Rp3.842.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.835.000</t>
+          <t>Rp4.335.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7390,14 +7390,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.225.000</t>
+          <t>Rp13.400.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp570.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.030.000</t>
+          <t>Rp9.255.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp8.540.000</t>
+          <t>Rp8.240.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.400.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.065.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.580.000</t>
+          <t>Rp1.740.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp15.540.000</t>
+          <t>Rp16.300.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.245.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-20.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp966.000</t>
+          <t>Rp1.136.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.280.000</t>
+          <t>Rp14.640.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.796.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.680.000</t>
+          <t>Rp5.280.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.276.987</t>
+          <t>Rp5.974.985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.224.000</t>
+          <t>Rp4.512.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.490.000</t>
+          <t>Rp13.240.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.064.000</t>
+          <t>Rp1.314.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.211.000</t>
+          <t>Rp3.549.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.410.000</t>
+          <t>Rp1.509.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.925.000</t>
+          <t>Rp2.755.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.285.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.024.000</t>
+          <t>Rp3.408.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.745.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.967.000</t>
+          <t>Rp8.667.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.475.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp1.590.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp7.720.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.274.000</t>
+          <t>Rp3.672.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp2.760.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>90</v>
       </c>
       <c r="D93" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp714.000</t>
+          <t>Rp764.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp2.140.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.600.000</t>
+          <t>Rp13.198.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.155.000</t>
+          <t>Rp7.290.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp746.000</t>
+          <t>Rp795.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.356.000</t>
+          <t>Rp2.754.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp13.050.000</t>
+          <t>Rp12.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp9.350.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp133.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp510.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp11.250.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp2.259.000</t>
+          <t>Rp2.853.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp10.050.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp32.300.000</t>
+          <t>Rp33.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.080.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.660.000</t>
+          <t>Rp11.860.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.415.000</t>
+          <t>Rp10.640.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp168.000</t>
+          <t>Rp237.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.155.000</t>
+          <t>Rp11.335.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6711,21 +6711,21 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.325.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp350.000</t>
+          <t>Rp175.000 - Rp385.000</t>
         </is>
       </c>
     </row>
@@ -6773,16 +6773,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.009.000</t>
+          <t>Rp8.426.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.550.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7207,21 +7207,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.335.000</t>
+          <t>Rp4.659.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7393,16 +7393,16 @@
         <v>78</v>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp7.630.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.400.000</t>
+          <t>Rp13.500.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.232.000</t>
+          <t>Rp4.672.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.075.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp18.375.000</t>
+          <t>Rp18.675.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.255.000</t>
+          <t>Rp9.755.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp23.600.000</t>
+          <t>Rp24.600.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp820.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.597.000</t>
+          <t>Rp5.368.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp16.300.000</t>
+          <t>Rp17.920.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.274.993</t>
+          <t>Rp4.524.993</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.442.000</t>
+          <t>Rp2.692.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.655.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.856.000</t>
+          <t>Rp4.836.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp796.000</t>
+          <t>Rp1.592.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-20.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.640.000</t>
+          <t>Rp15.840.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.689.000</t>
+          <t>Rp2.139.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.280.000</t>
+          <t>Rp4.560.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.974.985</t>
+          <t>Rp6.471.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.669.500</t>
+          <t>Rp10.604.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.512.000</t>
+          <t>Rp5.088.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,11 +978,11 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.240.000</t>
+          <t>Rp13.545.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp9.548.000</t>
+          <t>Rp9.848.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.408.000</t>
+          <t>Rp3.674.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.905.000</t>
+          <t>Rp4.535.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.667.000</t>
+          <t>Rp9.367.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp6.336.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.030.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp444.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp549.000</t>
+          <t>Rp749.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp397.000</t>
+          <t>Rp695.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp3.988.000</t>
+          <t>Rp4.786.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.984.000</t>
+          <t>Rp6.027.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp1.530.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp5.535.000</t>
+          <t>Rp5.290.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.672.000</t>
+          <t>Rp4.169.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp4.595.000</t>
+          <t>Rp4.775.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>90</v>
       </c>
       <c r="D93" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp764.000</t>
+          <t>Rp863.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp5.223.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.296.000</t>
+          <t>Rp1.377.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.198.000</t>
+          <t>Rp12.600.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp3.730.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.198.000</t>
+          <t>Rp2.098.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp2.295.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp9.867.000</t>
+          <t>Rp10.764.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp549.000</t>
+          <t>Rp749.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.754.000</t>
+          <t>Rp3.083.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp12.650.000</t>
+          <t>Rp13.700.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp3.852.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp9.252.000</t>
+          <t>Rp9.648.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp133.000</t>
+          <t>Rp248.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp1.160.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.130.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.960.000</t>
+          <t>Rp8.440.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.000.000</t>
+          <t>Rp31.450.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.640.000</t>
+          <t>Rp5.340.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.860.000</t>
+          <t>Rp12.060.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.640.000</t>
+          <t>Rp11.040.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp237.000</t>
+          <t>Rp574.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.335.000</t>
+          <t>Rp11.735.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp7.025.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.029.500</t>
+          <t>Rp15.304.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.106.000</t>
+          <t>Rp4.943.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.195.000</t>
+          <t>Rp4.470.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp10.050.000</t>
+          <t>Rp10.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.100.000</t>
+          <t>Rp19.700.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.659.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.130.000</t>
+          <t>Rp5.385.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp7.030.000</t>
+          <t>Rp8.030.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.500.000</t>
+          <t>Rp14.850.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp570.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp18.675.000</t>
+          <t>Rp20.075.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp24.600.000</t>
+          <t>Rp26.600.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp10.971.000</t>
+          <t>Rp11.320.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.765.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.838.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.335.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.368.000</t>
+          <t>Rp4.068.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp17.920.000</t>
+          <t>Rp18.320.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.080.000</t>
+          <t>Rp2.715.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.645.000</t>
+          <t>Rp2.930.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.180.000</t>
+          <t>Rp1.895.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.875.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-20.xlsx
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.945.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.755.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp4.905.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.367.000</t>
+          <t>Rp10.767.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.786.000</t>
+          <t>Rp5.185.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp1.605.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.175.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp449.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
     </row>
@@ -3943,16 +3943,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.385.000</t>
+          <t>Rp6.755.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp13.700.000</t>
+          <t>Rp13.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp11.650.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp10.600.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.344.000</t>
+          <t>Rp1.994.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.060.000</t>
+          <t>Rp11.980.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.735.000</t>
+          <t>Rp12.125.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.426.000</t>
+          <t>Rp9.134.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.842.000</t>
+          <t>Rp4.380.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.240.000</t>
+          <t>Rp1.340.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.850.000</t>
+          <t>Rp15.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.400.000</t>
+          <t>Rp11.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp370.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.068.000</t>
+          <t>Rp4.718.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.836.000</t>
+          <t>Rp4.637.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-20.xlsx
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.471.984</t>
+          <t>Rp6.323.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.604.500</t>
+          <t>Rp10.760.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.905.000</t>
+          <t>Rp4.745.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp2.735.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.662.500</t>
+          <t>Rp7.762.500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.605.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp100.000</t>
+          <t>Rp228.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp4.955.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.590.000</t>
+          <t>Rp2.690.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.630.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp10.050.000</t>
+          <t>Rp11.450.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.050.000</t>
+          <t>Rp18.782.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.340.000</t>
+          <t>Rp5.590.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.980.000</t>
+          <t>Rp12.180.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp574.000</t>
+          <t>Rp811.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp15.050.000</t>
+          <t>Rp15.175.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.755.000</t>
+          <t>Rp10.030.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp520.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.637.000</t>
+          <t>Rp4.736.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
